--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6761" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6727" uniqueCount="781">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1842,22 +1842,6 @@
     <t>Claim.accident.extension</t>
   </si>
   <si>
-    <t>Claim.accident.extension:VerdachtArbeitsSchuelerunfall</t>
-  </si>
-  <si>
-    <t>VerdachtArbeitsSchuelerunfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-VerdachtArbeitsSchuelerunfall}
-</t>
-  </si>
-  <si>
-    <t>Verdacht auf Arbeits- oder Schuelerunfall</t>
-  </si>
-  <si>
-    <t>MOPED Extension für den Verdacht auf einen Arbeits- oder Schuelerunfall.</t>
-  </si>
-  <si>
     <t>Claim.accident.modifierExtension</t>
   </si>
   <si>
@@ -1892,10 +1876,7 @@
     <t>Coverage may be dependant on the type of accident.</t>
   </si>
   <si>
-    <t>Type of accident: work place, auto, etc.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActIncidentCode</t>
+    <t>http://example.org/ValueSet/moped-VerdachtArbeitsSchuelerunfall-valueset</t>
   </si>
   <si>
     <t>Claim.accident.location[x]</t>
@@ -2759,12 +2740,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM191"/>
+  <dimension ref="A1:AM190"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.41015625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="26.45703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="48.5859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2787,7 +2768,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.1640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.04296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.97265625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -15301,7 +15282,7 @@
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15323,12 +15304,14 @@
         <v>134</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>135</v>
+        <v>272</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>19</v>
@@ -15365,14 +15348,16 @@
         <v>19</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC113" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD113" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>274</v>
@@ -15396,7 +15381,7 @@
         <v>19</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114">
@@ -15404,41 +15389,43 @@
         <v>584</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>586</v>
+        <v>134</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>587</v>
+        <v>277</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>19</v>
       </c>
@@ -15486,7 +15473,7 @@
         <v>19</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15507,50 +15494,50 @@
         <v>19</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>19</v>
+        <v>132</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>134</v>
+        <v>586</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>277</v>
+        <v>587</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>278</v>
+        <v>588</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>153</v>
+        <v>589</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>154</v>
+        <v>590</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>19</v>
@@ -15599,19 +15586,19 @@
         <v>19</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>279</v>
+        <v>585</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>19</v>
@@ -15620,15 +15607,15 @@
         <v>19</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15636,7 +15623,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>87</v>
@@ -15651,7 +15638,7 @@
         <v>19</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>591</v>
+        <v>178</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>592</v>
@@ -15659,11 +15646,9 @@
       <c r="M116" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>19</v>
@@ -15688,13 +15673,11 @@
         <v>19</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>19</v>
+        <v>595</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>19</v>
@@ -15712,10 +15695,10 @@
         <v>19</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>87</v>
@@ -15764,17 +15747,17 @@
         <v>19</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>178</v>
+        <v>597</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>19</v>
@@ -15799,13 +15782,13 @@
         <v>19</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>600</v>
+        <v>19</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>601</v>
+        <v>19</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>19</v>
@@ -15849,10 +15832,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15875,17 +15858,17 @@
         <v>19</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>19</v>
@@ -15934,7 +15917,7 @@
         <v>19</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15960,10 +15943,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15974,7 +15957,7 @@
         <v>76</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>19</v>
@@ -15986,17 +15969,17 @@
         <v>19</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>19</v>
@@ -16045,13 +16028,13 @@
         <v>19</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>19</v>
@@ -16071,10 +16054,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16085,7 +16068,7 @@
         <v>76</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>19</v>
@@ -16097,18 +16080,16 @@
         <v>19</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>613</v>
+        <v>266</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>614</v>
+        <v>267</v>
       </c>
       <c r="N120" s="2"/>
-      <c r="O120" t="s" s="2">
-        <v>615</v>
-      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>19</v>
       </c>
@@ -16156,19 +16137,19 @@
         <v>19</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>612</v>
+        <v>268</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>19</v>
@@ -16177,26 +16158,26 @@
         <v>19</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>19</v>
@@ -16208,15 +16189,17 @@
         <v>19</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>19</v>
@@ -16265,19 +16248,19 @@
         <v>19</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>269</v>
+        <v>19</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>19</v>
@@ -16291,14 +16274,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>150</v>
+        <v>276</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16311,24 +16294,26 @@
         <v>19</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="O122" s="2"/>
+      <c r="O122" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>19</v>
       </c>
@@ -16376,7 +16361,7 @@
         <v>19</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16397,50 +16382,48 @@
         <v>19</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>270</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>277</v>
+        <v>614</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>154</v>
+        <v>616</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>19</v>
@@ -16489,19 +16472,19 @@
         <v>19</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>279</v>
+        <v>613</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>19</v>
@@ -16510,15 +16493,15 @@
         <v>19</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16526,10 +16509,10 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>19</v>
@@ -16541,17 +16524,17 @@
         <v>19</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>383</v>
+        <v>158</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>620</v>
+        <v>165</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>621</v>
+        <v>166</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>622</v>
+        <v>167</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>19</v>
@@ -16600,13 +16583,13 @@
         <v>19</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>19</v>
@@ -16626,10 +16609,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16652,17 +16635,17 @@
         <v>19</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>158</v>
+        <v>383</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>165</v>
+        <v>619</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>166</v>
+        <v>620</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>167</v>
+        <v>621</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>19</v>
@@ -16711,7 +16694,7 @@
         <v>19</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16737,10 +16720,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16766,14 +16749,14 @@
         <v>383</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>19</v>
@@ -16822,7 +16805,7 @@
         <v>19</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16848,10 +16831,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16877,14 +16860,14 @@
         <v>383</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>19</v>
@@ -16933,7 +16916,7 @@
         <v>19</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -16959,10 +16942,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16988,14 +16971,14 @@
         <v>383</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>19</v>
@@ -17044,7 +17027,7 @@
         <v>19</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -17070,10 +17053,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17084,7 +17067,7 @@
         <v>76</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>19</v>
@@ -17096,17 +17079,17 @@
         <v>19</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>383</v>
+        <v>178</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>19</v>
@@ -17131,13 +17114,13 @@
         <v>19</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>19</v>
+        <v>638</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>19</v>
+        <v>639</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>19</v>
@@ -17155,13 +17138,13 @@
         <v>19</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>19</v>
@@ -17215,9 +17198,11 @@
       <c r="M130" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N130" s="2"/>
+      <c r="N130" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="O130" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>19</v>
@@ -17245,10 +17230,10 @@
         <v>193</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>19</v>
@@ -17292,14 +17277,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>19</v>
+        <v>648</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17321,16 +17306,16 @@
         <v>178</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>19</v>
@@ -17358,10 +17343,10 @@
         <v>193</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>19</v>
@@ -17379,7 +17364,7 @@
         <v>19</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17405,14 +17390,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17434,17 +17419,13 @@
         <v>178</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O132" t="s" s="2">
         <v>658</v>
       </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>19</v>
       </c>
@@ -17470,11 +17451,9 @@
       <c r="X132" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y132" t="s" s="2">
-        <v>659</v>
-      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>19</v>
@@ -17492,7 +17471,7 @@
         <v>19</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17518,21 +17497,21 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>662</v>
+        <v>19</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>19</v>
@@ -17544,16 +17523,18 @@
         <v>19</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>178</v>
+        <v>660</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M133" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>19</v>
       </c>
@@ -17577,11 +17558,13 @@
         <v>19</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y133" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z133" t="s" s="2">
-        <v>660</v>
+        <v>19</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>19</v>
@@ -17599,13 +17582,13 @@
         <v>19</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>19</v>
@@ -17625,10 +17608,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17651,17 +17634,19 @@
         <v>19</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>19</v>
@@ -17686,13 +17671,13 @@
         <v>19</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>19</v>
+        <v>669</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>19</v>
+        <v>670</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>19</v>
@@ -17710,7 +17695,7 @@
         <v>19</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17736,10 +17721,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17765,16 +17750,16 @@
         <v>178</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>19</v>
@@ -17802,10 +17787,10 @@
         <v>193</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>19</v>
@@ -17823,7 +17808,7 @@
         <v>19</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17849,10 +17834,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17863,7 +17848,7 @@
         <v>76</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>19</v>
@@ -17875,17 +17860,15 @@
         <v>19</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>178</v>
+        <v>440</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N136" t="s" s="2">
         <v>680</v>
       </c>
+      <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
         <v>681</v>
       </c>
@@ -17912,13 +17895,13 @@
         <v>19</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>682</v>
+        <v>19</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>683</v>
+        <v>19</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>19</v>
@@ -17936,13 +17919,13 @@
         <v>19</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>19</v>
@@ -17954,7 +17937,7 @@
         <v>19</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>19</v>
+        <v>216</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>19</v>
@@ -17962,10 +17945,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17988,17 +17971,17 @@
         <v>19</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>440</v>
+        <v>683</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>19</v>
@@ -18023,13 +18006,13 @@
         <v>19</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>19</v>
+        <v>687</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>19</v>
+        <v>688</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>19</v>
@@ -18047,7 +18030,7 @@
         <v>19</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18065,7 +18048,7 @@
         <v>19</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>19</v>
@@ -18073,10 +18056,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18099,17 +18082,17 @@
         <v>19</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>689</v>
+        <v>602</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>690</v>
+        <v>603</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>691</v>
+        <v>604</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>692</v>
+        <v>605</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>19</v>
@@ -18134,13 +18117,13 @@
         <v>19</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>693</v>
+        <v>19</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>694</v>
+        <v>19</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>19</v>
@@ -18158,7 +18141,7 @@
         <v>19</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -18176,7 +18159,7 @@
         <v>19</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>19</v>
@@ -18184,10 +18167,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18210,17 +18193,17 @@
         <v>19</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>608</v>
+        <v>691</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>609</v>
+        <v>692</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>610</v>
+        <v>693</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>611</v>
+        <v>694</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>19</v>
@@ -18269,7 +18252,7 @@
         <v>19</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -18295,10 +18278,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18321,17 +18304,17 @@
         <v>19</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>19</v>
@@ -18380,7 +18363,7 @@
         <v>19</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18406,10 +18389,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18432,15 +18415,17 @@
         <v>19</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>608</v>
+        <v>700</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
         <v>704</v>
       </c>
@@ -18491,7 +18476,7 @@
         <v>19</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18543,19 +18528,17 @@
         <v>19</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" s="2"/>
+      <c r="O142" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>19</v>
@@ -18630,10 +18613,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18656,17 +18639,19 @@
         <v>19</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>19</v>
@@ -18715,7 +18700,7 @@
         <v>19</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -18741,10 +18726,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18755,7 +18740,7 @@
         <v>76</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>19</v>
@@ -18767,19 +18752,17 @@
         <v>19</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>608</v>
+        <v>531</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>716</v>
+        <v>532</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>719</v>
+        <v>534</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>19</v>
@@ -18828,13 +18811,13 @@
         <v>19</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>19</v>
@@ -18854,10 +18837,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18880,18 +18863,16 @@
         <v>19</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>531</v>
+        <v>259</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>532</v>
+        <v>716</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>533</v>
+        <v>717</v>
       </c>
       <c r="N145" s="2"/>
-      <c r="O145" t="s" s="2">
-        <v>534</v>
-      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>19</v>
       </c>
@@ -18939,7 +18920,7 @@
         <v>19</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
@@ -18965,10 +18946,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18979,7 +18960,7 @@
         <v>76</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>19</v>
@@ -18991,13 +18972,13 @@
         <v>19</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>722</v>
+        <v>266</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>723</v>
+        <v>267</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -19048,19 +19029,19 @@
         <v>19</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>721</v>
+        <v>268</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>19</v>
@@ -19069,26 +19050,26 @@
         <v>19</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>19</v>
@@ -19100,15 +19081,17 @@
         <v>19</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N147" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>19</v>
@@ -19157,19 +19140,19 @@
         <v>19</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>269</v>
+        <v>19</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>19</v>
@@ -19183,14 +19166,14 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>150</v>
+        <v>276</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -19203,24 +19186,26 @@
         <v>19</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K148" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="O148" s="2"/>
+      <c r="O148" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>19</v>
       </c>
@@ -19268,7 +19253,7 @@
         <v>19</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19289,23 +19274,23 @@
         <v>19</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>270</v>
+        <v>132</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>77</v>
@@ -19314,25 +19299,25 @@
         <v>19</v>
       </c>
       <c r="I149" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>134</v>
+        <v>722</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>277</v>
+        <v>723</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>278</v>
+        <v>724</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>153</v>
+        <v>725</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>154</v>
+        <v>726</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>19</v>
@@ -19357,13 +19342,11 @@
         <v>19</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>19</v>
+        <v>727</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>19</v>
@@ -19381,10 +19364,10 @@
         <v>19</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>279</v>
+        <v>721</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -19393,7 +19376,7 @@
         <v>19</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>19</v>
@@ -19402,15 +19385,15 @@
         <v>19</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19418,7 +19401,7 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>77</v>
@@ -19433,7 +19416,7 @@
         <v>19</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>728</v>
+        <v>178</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>729</v>
@@ -19441,11 +19424,9 @@
       <c r="M150" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="N150" t="s" s="2">
-        <v>731</v>
-      </c>
+      <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>19</v>
@@ -19474,7 +19455,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>19</v>
@@ -19492,10 +19473,10 @@
         <v>19</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -19518,10 +19499,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19544,17 +19525,19 @@
         <v>19</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>178</v>
+        <v>335</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>735</v>
+        <v>336</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O151" t="s" s="2">
-        <v>732</v>
+        <v>339</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>19</v>
@@ -19579,11 +19562,13 @@
         <v>19</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y151" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z151" t="s" s="2">
-        <v>737</v>
+        <v>19</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>19</v>
@@ -19601,7 +19586,7 @@
         <v>19</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19616,7 +19601,7 @@
         <v>99</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>19</v>
+        <v>733</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>19</v>
@@ -19627,10 +19612,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19653,19 +19638,17 @@
         <v>19</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>335</v>
+        <v>259</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>336</v>
+        <v>607</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>735</v>
+      </c>
+      <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>339</v>
+        <v>609</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>19</v>
@@ -19714,7 +19697,7 @@
         <v>19</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
@@ -19729,7 +19712,7 @@
         <v>99</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>739</v>
+        <v>19</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>19</v>
@@ -19740,10 +19723,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19754,7 +19737,7 @@
         <v>76</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>19</v>
@@ -19766,18 +19749,16 @@
         <v>19</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>613</v>
+        <v>266</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>741</v>
+        <v>267</v>
       </c>
       <c r="N153" s="2"/>
-      <c r="O153" t="s" s="2">
-        <v>615</v>
-      </c>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>19</v>
       </c>
@@ -19825,19 +19806,19 @@
         <v>19</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>740</v>
+        <v>268</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>19</v>
@@ -19846,26 +19827,26 @@
         <v>19</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>19</v>
@@ -19877,15 +19858,17 @@
         <v>19</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N154" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>19</v>
@@ -19934,19 +19917,19 @@
         <v>19</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>269</v>
+        <v>19</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>19</v>
@@ -19960,14 +19943,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>150</v>
+        <v>276</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -19980,24 +19963,26 @@
         <v>19</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K155" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="O155" s="2"/>
+      <c r="O155" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>19</v>
       </c>
@@ -20045,7 +20030,7 @@
         <v>19</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -20066,50 +20051,48 @@
         <v>19</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>270</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I156" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>277</v>
+        <v>614</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>154</v>
+        <v>616</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>19</v>
@@ -20158,19 +20141,19 @@
         <v>19</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>279</v>
+        <v>739</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>19</v>
@@ -20179,15 +20162,15 @@
         <v>19</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20195,10 +20178,10 @@
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>19</v>
@@ -20210,17 +20193,17 @@
         <v>19</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>383</v>
+        <v>158</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>620</v>
+        <v>165</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>621</v>
+        <v>166</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>622</v>
+        <v>167</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>19</v>
@@ -20269,13 +20252,13 @@
         <v>19</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>19</v>
@@ -20295,10 +20278,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20309,7 +20292,7 @@
         <v>76</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>19</v>
@@ -20321,17 +20304,17 @@
         <v>19</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>165</v>
+        <v>635</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>166</v>
+        <v>636</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>167</v>
+        <v>637</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>19</v>
@@ -20356,13 +20339,13 @@
         <v>19</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>19</v>
+        <v>638</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>19</v>
+        <v>639</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>19</v>
@@ -20380,13 +20363,13 @@
         <v>19</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>19</v>
@@ -20406,10 +20389,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20440,9 +20423,11 @@
       <c r="M159" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N159" s="2"/>
+      <c r="N159" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="O159" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>19</v>
@@ -20470,10 +20455,10 @@
         <v>193</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>19</v>
@@ -20491,7 +20476,7 @@
         <v>19</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20517,14 +20502,14 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>19</v>
+        <v>648</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -20546,16 +20531,16 @@
         <v>178</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>19</v>
@@ -20583,10 +20568,10 @@
         <v>193</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>19</v>
@@ -20604,7 +20589,7 @@
         <v>19</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20630,14 +20615,14 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -20659,17 +20644,13 @@
         <v>178</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O161" t="s" s="2">
         <v>658</v>
       </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>19</v>
       </c>
@@ -20695,11 +20676,9 @@
       <c r="X161" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y161" t="s" s="2">
-        <v>659</v>
-      </c>
+      <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>19</v>
@@ -20717,7 +20696,7 @@
         <v>19</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20743,21 +20722,21 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>662</v>
+        <v>19</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>19</v>
@@ -20772,13 +20751,17 @@
         <v>178</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>663</v>
+        <v>746</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>19</v>
       </c>
@@ -20804,9 +20787,11 @@
       <c r="X162" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y162" s="2"/>
+      <c r="Y162" t="s" s="2">
+        <v>669</v>
+      </c>
       <c r="Z162" t="s" s="2">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>19</v>
@@ -20824,13 +20809,13 @@
         <v>19</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>19</v>
@@ -20850,10 +20835,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20879,16 +20864,16 @@
         <v>178</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>752</v>
+        <v>672</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>753</v>
+        <v>674</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>19</v>
@@ -20916,10 +20901,10 @@
         <v>193</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>19</v>
@@ -20937,7 +20922,7 @@
         <v>19</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -20963,10 +20948,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20977,7 +20962,7 @@
         <v>76</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>19</v>
@@ -20989,19 +20974,17 @@
         <v>19</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>178</v>
+        <v>602</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>678</v>
+        <v>603</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>680</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>681</v>
+        <v>605</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>19</v>
@@ -21026,13 +21009,13 @@
         <v>19</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>682</v>
+        <v>19</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>683</v>
+        <v>19</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>19</v>
@@ -21050,13 +21033,13 @@
         <v>19</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>19</v>
@@ -21076,10 +21059,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21102,17 +21085,17 @@
         <v>19</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>608</v>
+        <v>691</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>609</v>
+        <v>692</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>610</v>
+        <v>693</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>611</v>
+        <v>694</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>19</v>
@@ -21161,7 +21144,7 @@
         <v>19</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -21187,10 +21170,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21213,17 +21196,17 @@
         <v>19</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>19</v>
@@ -21272,7 +21255,7 @@
         <v>19</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -21298,10 +21281,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21324,15 +21307,17 @@
         <v>19</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>608</v>
+        <v>700</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
         <v>704</v>
       </c>
@@ -21383,7 +21368,7 @@
         <v>19</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21409,10 +21394,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21435,19 +21420,17 @@
         <v>19</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L168" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="M168" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" s="2"/>
+      <c r="O168" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>19</v>
@@ -21496,7 +21479,7 @@
         <v>19</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -21522,10 +21505,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21548,17 +21531,19 @@
         <v>19</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="N169" s="2"/>
-      <c r="O169" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>19</v>
@@ -21607,7 +21592,7 @@
         <v>19</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21633,10 +21618,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21647,7 +21632,7 @@
         <v>76</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>19</v>
@@ -21659,19 +21644,17 @@
         <v>19</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>608</v>
+        <v>531</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>716</v>
+        <v>532</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>719</v>
+        <v>534</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>19</v>
@@ -21720,13 +21703,13 @@
         <v>19</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>19</v>
@@ -21746,10 +21729,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21772,17 +21755,17 @@
         <v>19</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>531</v>
+        <v>259</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>532</v>
+        <v>607</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>533</v>
+        <v>735</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>534</v>
+        <v>609</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>19</v>
@@ -21831,7 +21814,7 @@
         <v>19</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>76</v>
@@ -21857,10 +21840,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21871,7 +21854,7 @@
         <v>76</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>19</v>
@@ -21883,18 +21866,16 @@
         <v>19</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>613</v>
+        <v>266</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>741</v>
+        <v>267</v>
       </c>
       <c r="N172" s="2"/>
-      <c r="O172" t="s" s="2">
-        <v>615</v>
-      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>19</v>
       </c>
@@ -21942,19 +21923,19 @@
         <v>19</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>763</v>
+        <v>268</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>19</v>
@@ -21963,26 +21944,26 @@
         <v>19</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>19</v>
@@ -21994,15 +21975,17 @@
         <v>19</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N173" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>19</v>
@@ -22051,19 +22034,19 @@
         <v>19</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>269</v>
+        <v>19</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>19</v>
@@ -22077,14 +22060,14 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>150</v>
+        <v>276</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -22097,24 +22080,26 @@
         <v>19</v>
       </c>
       <c r="I174" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K174" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="O174" s="2"/>
+      <c r="O174" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>19</v>
       </c>
@@ -22162,7 +22147,7 @@
         <v>19</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -22183,50 +22168,48 @@
         <v>19</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>270</v>
+        <v>132</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>277</v>
+        <v>614</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" t="s" s="2">
-        <v>154</v>
+        <v>616</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>19</v>
@@ -22275,19 +22258,19 @@
         <v>19</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>279</v>
+        <v>761</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>19</v>
@@ -22296,15 +22279,15 @@
         <v>19</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22312,10 +22295,10 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>19</v>
@@ -22327,17 +22310,17 @@
         <v>19</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>383</v>
+        <v>158</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>620</v>
+        <v>165</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>621</v>
+        <v>166</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>622</v>
+        <v>167</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>19</v>
@@ -22386,13 +22369,13 @@
         <v>19</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>19</v>
@@ -22412,10 +22395,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22426,7 +22409,7 @@
         <v>76</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>19</v>
@@ -22438,17 +22421,17 @@
         <v>19</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>165</v>
+        <v>635</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>166</v>
+        <v>636</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" t="s" s="2">
-        <v>167</v>
+        <v>637</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>19</v>
@@ -22473,13 +22456,13 @@
         <v>19</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>19</v>
+        <v>638</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>19</v>
+        <v>639</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>19</v>
@@ -22497,13 +22480,13 @@
         <v>19</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>19</v>
@@ -22523,10 +22506,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22557,9 +22540,11 @@
       <c r="M178" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N178" s="2"/>
+      <c r="N178" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="O178" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>19</v>
@@ -22587,10 +22572,10 @@
         <v>193</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>19</v>
@@ -22608,7 +22593,7 @@
         <v>19</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22634,10 +22619,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22663,16 +22648,16 @@
         <v>178</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>19</v>
@@ -22700,10 +22685,10 @@
         <v>193</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>19</v>
@@ -22721,7 +22706,7 @@
         <v>19</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22747,14 +22732,14 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>19</v>
+        <v>656</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -22776,17 +22761,13 @@
         <v>178</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O180" t="s" s="2">
         <v>658</v>
       </c>
+      <c r="N180" s="2"/>
+      <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>19</v>
       </c>
@@ -22812,11 +22793,9 @@
       <c r="X180" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y180" t="s" s="2">
-        <v>659</v>
-      </c>
+      <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>19</v>
@@ -22834,7 +22813,7 @@
         <v>19</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22860,21 +22839,21 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>662</v>
+        <v>19</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>19</v>
@@ -22889,13 +22868,17 @@
         <v>178</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>663</v>
+        <v>746</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N181" s="2"/>
-      <c r="O181" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="P181" t="s" s="2">
         <v>19</v>
       </c>
@@ -22921,9 +22904,11 @@
       <c r="X181" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y181" s="2"/>
+      <c r="Y181" t="s" s="2">
+        <v>669</v>
+      </c>
       <c r="Z181" t="s" s="2">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>19</v>
@@ -22941,13 +22926,13 @@
         <v>19</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>19</v>
@@ -22967,10 +22952,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22996,16 +22981,16 @@
         <v>178</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>752</v>
+        <v>672</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>753</v>
+        <v>674</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>19</v>
@@ -23033,10 +23018,10 @@
         <v>193</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>19</v>
@@ -23054,7 +23039,7 @@
         <v>19</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -23080,10 +23065,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23094,7 +23079,7 @@
         <v>76</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>19</v>
@@ -23106,19 +23091,17 @@
         <v>19</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>178</v>
+        <v>602</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>678</v>
+        <v>603</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>680</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>681</v>
+        <v>605</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>19</v>
@@ -23143,13 +23126,13 @@
         <v>19</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>682</v>
+        <v>19</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>683</v>
+        <v>19</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>19</v>
@@ -23167,13 +23150,13 @@
         <v>19</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>19</v>
@@ -23193,10 +23176,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23219,17 +23202,17 @@
         <v>19</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>608</v>
+        <v>691</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>609</v>
+        <v>692</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>610</v>
+        <v>693</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>611</v>
+        <v>694</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>19</v>
@@ -23278,7 +23261,7 @@
         <v>19</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23304,10 +23287,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23330,17 +23313,17 @@
         <v>19</v>
       </c>
       <c r="K185" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>19</v>
@@ -23389,7 +23372,7 @@
         <v>19</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23415,10 +23398,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23441,15 +23424,17 @@
         <v>19</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>608</v>
+        <v>700</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
         <v>704</v>
       </c>
@@ -23500,7 +23485,7 @@
         <v>19</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>
@@ -23526,10 +23511,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23552,19 +23537,17 @@
         <v>19</v>
       </c>
       <c r="K187" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L187" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="L187" t="s" s="2">
+      <c r="M187" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" s="2"/>
+      <c r="O187" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>19</v>
@@ -23613,7 +23596,7 @@
         <v>19</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>76</v>
@@ -23639,10 +23622,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23665,17 +23648,19 @@
         <v>19</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="N188" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="N188" s="2"/>
-      <c r="O188" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>19</v>
@@ -23724,7 +23709,7 @@
         <v>19</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>76</v>
@@ -23750,10 +23735,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23764,7 +23749,7 @@
         <v>76</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>19</v>
@@ -23776,19 +23761,17 @@
         <v>19</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>608</v>
+        <v>531</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>716</v>
+        <v>532</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>719</v>
+        <v>534</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>19</v>
@@ -23837,13 +23820,13 @@
         <v>19</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>19</v>
@@ -23863,10 +23846,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23877,7 +23860,7 @@
         <v>76</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>19</v>
@@ -23889,17 +23872,17 @@
         <v>19</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>531</v>
+        <v>602</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>532</v>
+        <v>778</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>533</v>
+        <v>779</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>534</v>
+        <v>780</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>19</v>
@@ -23948,13 +23931,13 @@
         <v>19</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>19</v>
@@ -23969,117 +23952,6 @@
         <v>19</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="N191" s="2"/>
-      <c r="O191" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM191" t="s" s="2">
         <v>19</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedVAERequest</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedVAERequest</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -461,7 +461,7 @@
     <t>Verlaengerungstage</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-verlaengerungstage}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-verlaengerungstage}
 </t>
   </si>
   <si>
@@ -474,7 +474,7 @@
     <t>Sonderklasse</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-sonderklasse}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-sonderklasse}
 </t>
   </si>
   <si>
@@ -898,7 +898,7 @@
     <t>Claim.related.claim</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedVAERequest)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedVAERequest)
 </t>
   </si>
   <si>
@@ -1090,7 +1090,7 @@
     <t>MopedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -1103,7 +1103,7 @@
     <t>TransferEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedTransferEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedTransferEncounter)
 </t>
   </si>
   <si>
@@ -1765,7 +1765,7 @@
     <t>Claim.insurance.coverage</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedCoverage)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedCoverage)
 </t>
   </si>
   <si>
@@ -1876,7 +1876,7 @@
     <t>Coverage may be dependant on the type of accident.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-VerdachtArbeitsSchuelerunfall-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-VerdachtArbeitsSchuelerunfall-valueset</t>
   </si>
   <si>
     <t>Claim.accident.location[x]</t>
@@ -2768,7 +2768,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.04296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.97265625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedVAERequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
